--- a/data/trans_camb/P1435-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1435-Edad-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-5,32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-6,89</t>
+          <t>-5,32</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,37; -1,89</t>
+          <t>-10,81; -1,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,97; -7,22</t>
+          <t>-15,19; -7,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -0,32</t>
+          <t>-10,93; 0,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,37; -1,89</t>
+          <t>-10,81; -1,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,97; -7,22</t>
+          <t>-15,19; -7,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -0,32</t>
+          <t>-10,93; 0,83</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-41,5%</t>
+          <t>-32,03%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-41,5%</t>
+          <t>-32,03%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-55,04; -11,75</t>
+          <t>-56,73; -11,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,4; -47,75</t>
+          <t>-80,11; -48,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,47; -1,91</t>
+          <t>-58,52; 7,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,04; -11,75</t>
+          <t>-56,73; -11,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,4; -47,75</t>
+          <t>-80,11; -48,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,47; -1,91</t>
+          <t>-58,52; 7,01</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,53</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,53</t>
+          <t>-1,58</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -5,11</t>
+          <t>-12,28; -5,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -7,37</t>
+          <t>-14,2; -7,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 40,2</t>
+          <t>-5,97; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,15; -5,11</t>
+          <t>-12,28; -5,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -7,37</t>
+          <t>-14,2; -7,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 40,2</t>
+          <t>-5,97; 2,52</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>-10,59%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>-10,59%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,04; -40,82</t>
+          <t>-72,23; -40,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-83,46; -58,58</t>
+          <t>-82,82; -57,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 288,97</t>
+          <t>-35,75; 19,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,04; -40,82</t>
+          <t>-72,23; -40,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,46; -58,58</t>
+          <t>-82,82; -57,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 288,97</t>
+          <t>-35,75; 19,38</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,89</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,23</t>
+          <t>-5,21; 0,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -4,9</t>
+          <t>-9,73; -4,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,0</t>
+          <t>-0,31; 6,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,23</t>
+          <t>-5,21; 0,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,91; -4,9</t>
+          <t>-9,73; -4,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 6,0</t>
+          <t>-0,31; 6,32</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,69; 5,25</t>
+          <t>-50,34; 10,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,26; -62,15</t>
+          <t>-89,38; -62,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 79,88</t>
+          <t>-2,7; 88,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,69; 5,25</t>
+          <t>-50,34; 10,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,26; -62,15</t>
+          <t>-89,38; -62,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 79,88</t>
+          <t>-2,7; 88,31</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,62</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,04</t>
+          <t>-4,02; -0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,4</t>
+          <t>-4,19; -0,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,05</t>
+          <t>0,34; 4,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,04</t>
+          <t>-4,02; -0,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,4</t>
+          <t>-4,19; -0,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 4,05</t>
+          <t>0,34; 4,78</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 10,18</t>
+          <t>-80,88; 10,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-81,02; -8,74</t>
+          <t>-82,76; -6,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 164,67</t>
+          <t>5,16; 196,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 10,18</t>
+          <t>-80,88; 10,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,02; -8,74</t>
+          <t>-82,76; -6,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 164,67</t>
+          <t>5,16; 196,97</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,34</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; -0,2</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; -0,2</t>
+          <t>-1,96; -0,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,33</t>
+          <t>-1,67; 0,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; -0,2</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,15; -0,2</t>
+          <t>-1,96; -0,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,33</t>
+          <t>-1,67; 0,35</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-44,07%</t>
+          <t>-46,74%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-44,07%</t>
+          <t>-46,74%</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,26</t>
+          <t>-2,53; -0,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; -0,26</t>
+          <t>-2,48; -0,26</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,26</t>
+          <t>-2,33; -0,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,26</t>
+          <t>-2,53; -0,43</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; -0,26</t>
+          <t>-2,48; -0,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; -0,26</t>
+          <t>-2,33; -0,26</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>-2,61; 0,0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>-2,61; 0,0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>-2,56; 0,0</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 0,0</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 0,0</t>
-        </is>
-      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>-2,61; 0,0</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>-2,61; 0,0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>-2,56; 0,0</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 0,0</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 0,0</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-1,55</t>
         </is>
       </c>
     </row>
@@ -1726,32 +1726,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -2,8</t>
+          <t>-4,98; -2,85</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -4,79</t>
+          <t>-6,88; -4,87</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,29</t>
+          <t>-2,74; -0,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -2,8</t>
+          <t>-4,98; -2,85</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -4,79</t>
+          <t>-6,88; -4,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,29</t>
+          <t>-2,74; -0,31</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-20,14%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-5,07%</t>
+          <t>-20,14%</t>
         </is>
       </c>
     </row>
@@ -1802,32 +1802,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-58,64; -38,93</t>
+          <t>-59,39; -39,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-81,24; -68,31</t>
+          <t>-81,64; -68,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 85,98</t>
+          <t>-32,82; -4,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-58,64; -38,93</t>
+          <t>-59,39; -39,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-81,24; -68,31</t>
+          <t>-81,64; -68,02</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-33,52; 85,98</t>
+          <t>-32,82; -4,27</t>
         </is>
       </c>
     </row>
